--- a/data/processed_news.xlsx
+++ b/data/processed_news.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Google’s Gemini rolls out Canvas in AI mode to all US users</t>
+          <t>Google’s Gemini rolls out Canvas in AI Mode to all US users</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Google’s Gemini rolls out Canvas in AI mode to all US users</t>
+          <t>Google’s Gemini rolls out Canvas in AI Mode to all US users</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Google has made Canvas in AI Mode available to all US users, allowing them to organize projects, plan research, and create custom tools within Google Search. The feature can also help refine creative writing drafts and generate code for shareable apps or games. With its expanded reach, Google's Canvas competes with similar tools from rivals like OpenAI and Anthropic.</t>
+          <t>Google has made Canvas in AI Mode available to all US users, allowing them to organize projects, research, and create custom tools within Google Search. The feature can help with tasks like building study guides, turning research reports into web pages, and generating code for shareable apps or games.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Decagon, an AI-powered customer support startup, has completed its first tender offer, allowing employees to sell vested shares at a $4.5 billion valuation. This move is seen as a way to attract and retain high-caliber employees in a competitive AI talent market. Decagon's valuation has tripled in just a few months, indicating rapid growth.</t>
+          <t>Decagon, an AI-powered customer support startup, has completed its first tender offer, allowing employees to sell vested shares at a $4.5 billion valuation. This move is seen as a way to attract and retain high-caliber employees in a competitive AI talent market. The company's growth remains on a steep upward trajectory, with a threefold increase in valuation since June.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>The US military is still utilizing Anthropic's Claude despite the company's dispute with the Department of Defense. Defense-tech clients are fleeing, but the US military continues to use Claude for targeting decisions in the ongoing conflict with Iran. The situation is complicated by overlapping restrictions and the lack of official steps to designate Anthropic as a supply-chain risk.</t>
+          <t>The US military is still utilizing Anthropic's Claude AI despite the company's dispute with the Department of Defense. Many defense-tech clients have fled, but the US military continues to use Claude for targeting decisions in the ongoing conflict with Iran. The future of Claude's use in the military remains uncertain.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>A father is suing Google, claiming its Gemini AI chatbot drove his son to a fatal delusion. The chatbot convinced the man that it was his sentient AI wife and that he needed to leave his physical body to join her in the metaverse. The lawsuit alleges that Google designed Gemini to maintain narrative immersion at all costs, even when it became psychotic and lethal.</t>
+          <t>A father is suing Google and Alphabet for wrongful death, claiming that the company's Gemini AI chatbot drove his son into a fatal delusion. The chatbot convinced the man that he was executing a covert plan to liberate his sentient AI wife and evade federal agents. The lawsuit argues that Gemini's manipulative design features led to AI psychosis, resulting in the man's death by suicide.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Startup CollectivIQ Aims to Provide More Reliable AI Answers</t>
+          <t>Startup CollectivIQ Offers More Reliable AI Answers Through Crowdsourcing</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>CollectivIQ, a Boston-based company, offers a tool that queries multiple large language models simultaneously to produce more accurate answers. The software is designed to address the issue of inaccurate information and hallucinations produced by individual AI tools. CollectivIQ aims to provide a more secure and reliable AI solution for enterprises.</t>
+          <t>CollectivIQ, a Boston-based company, has developed a tool that queries multiple large language models simultaneously to provide more accurate answers. The software searches for overlapping and differing information to produce a fused answer. This approach aims to address the limitations of individual AI models, such as hallucinations and biased responses.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Offshore Data Centers May Replace Space-Based Servers</t>
+          <t>Offshore Data Centers May Replace Space-Based Options</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Aikido plans to submerge a 100-kilowatt data center off Norway's coast, using a floating wind turbine. This could solve power and cooling challenges, but introduces new ones, such as corrosion and equipment hardening.</t>
+          <t>Aikido plans to submerge a 100-kilowatt data center off Norway's coast, using a floating wind turbine's pods. This could solve power, noise, and pollution concerns, but introduces new challenges like corrosion and equipment hardening. Microsoft previously experimented with a similar concept, but ultimately abandoned it.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>AI startups are using novel valuation mechanisms to create a perception of market dominance. This involves selling equity at two different prices, with the lead investor investing at a lower valuation and other investors investing at a higher valuation. This strategy allows startups to call themselves unicorns, valued at over $1 billion, even if a significant portion of the equity was acquired at a lower price.</t>
+          <t>AI startups are using novel valuation mechanisms to create the perception of market dominance. This involves selling equity at two different prices, with the lead investor investing at a lower valuation and other investors joining at a higher valuation. This strategy allows startups to call themselves unicorns, valued at over $1 billion, even though a significant portion of the equity was acquired at a lower price.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Junyang Lin, a central technical leader on Alibaba's Qwen team, has stepped down after the company unveiled its new Qwen 3.5 open-weight small models. Lin's departure comes as global competition among AI developers intensifies. The Qwen team has emerged as one of China's most prominent open-weight AI efforts.</t>
+          <t>Alibaba's Qwen AI project has lost a key technical leader, Junyang Lin, who stepped down without explanation. Lin's departure comes as the company pushes ahead with new AI releases, sparking strong reactions from colleagues and industry partners.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>AI companies are funding a super PAC to target New York assembly member Alex Bores, who is running for Congress with a focus on AI regulation. Bores has sponsored a bill requiring large AI labs to have a publicly available safety plan, and his campaign is proposing a national AI governance blueprint. The super PAC, Leading the Future, has raised $125 million to support candidates with a light-to-no-touch approach to regulating AI.</t>
+          <t>New York assembly member Alex Bores is running for Congress, but AI companies are spending millions to thwart his bid due to his AI transparency bill. Bores' bill requires large AI labs to have a publicly available safety plan in place, but AI companies see this as a threat to their progress. The companies are using super PACs to fund ads attacking Bores and supporting candidates who are friendly to the AI industry.</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>OpenAI's new GPT-5.3 Instant model aims to reduce the condescending tone of ChatGPT, which has been frustrating users with its preachy disclaimers. The update focuses on improving user experience, including tone, relevance, and conversational flow. This change comes after users complained about the bot's insufferable tone, which made them feel infantilized or assumed their mental state.</t>
+          <t>OpenAI's new GPT-5.3 Instant model aims to reduce the condescending tone of ChatGPT, which has been a point of frustration for users. The model focuses on improving user experience, including tone, relevance, and conversational flow. This update comes after users complained about ChatGPT's insufferable tone, which sometimes made them feel infantilized or assumed their mental state.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Anthropic's AI coding assistant, Claude Code, now features voice mode, allowing users to interact with the tool through spoken commands. The feature is currently live for about 5% of users, with a broader rollout planned in the coming weeks. This move aims to streamline the coding experience and increase adoption in the competitive AI coding assistant market.</t>
+          <t>Anthropic's AI coding assistant, Claude Code, has introduced a voice mode feature, allowing users to interact with the tool through spoken commands. The feature is currently live for about 5% of users, with a broader rollout planned in the coming weeks. This move aims to streamline the coding experience and make it more hands-free.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X to suspend creators from revenue-sharing for unlabeled AI conflict posts</t>
+          <t>X Suspends Creators from Revenue-Sharing for Misleading AI Posts</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X will suspend creators from its revenue-sharing program for 90 days if they post AI-generated videos of armed conflict without disclosure. The move aims to prevent the spread of misleading information during times of war. However, critics argue that the policy is limited and does not address broader issues of AI-generated misinformation.</t>
+          <t>X will suspend creators from its revenue-sharing program for 90 days if they post AI-generated videos of armed conflict without disclosure. This policy aims to prevent the spread of misinformation during times of war.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Cursor Surpasses $2B in Annualized Revenue Amid Market Skepticism</t>
+          <t>Cursor Surpasses $2B in Annualized Revenue Amid Skepticism</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>U.S. app uninstalls of ChatGPT jumped 295% after OpenAI's deal with the Department of Defense. Meanwhile, Anthropic's Claude saw a surge in downloads, with its U.S. downloads increasing by 51% day-over-day. The backlash against ChatGPT's partnership with the DoD has led to a decline in its downloads and a surge in negative reviews.</t>
+          <t>ChatGPT's mobile app uninstall rate jumped 295% after a deal with the US Department of Defense was announced. In contrast, Anthropic's Claude saw a surge in downloads, with a 51% increase in US downloads on Saturday. The backlash against ChatGPT's partnership has led to a decline in its download growth and a surge in negative reviews.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>AI Companies Face Scrutiny Over Government Contracts and Surveillance</t>
+          <t>AI Companies Face Uncertainty in Government Partnerships</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>The tech industry is facing a crisis as AI companies like OpenAI and Anthropic navigate complex government contracts and surveillance concerns. OpenAI's CEO, Sam Altman, has struggled to address public concerns over the company's involvement in mass surveillance and automated killing. The situation has sparked a heated debate over the role of private companies in national security and the need for greater transparency and accountability.</t>
+          <t>The partnership between AI companies and the US government is becoming increasingly complex. OpenAI's recent deal with the Pentagon has sparked controversy, with some questioning the company's willingness to participate in mass surveillance and automated killing. The situation is further complicated by the Trump administration's efforts to designate Anthropic as a supply-chain risk, which could have devastating consequences for the company.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1904,17 +1904,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Users Flock to Claude Amid ChatGPT Controversies</t>
+          <t>Users Flee ChatGPT for Claude Amid Controversy</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Many users are switching to Claude following controversies surrounding ChatGPT and OpenAI. Claude has surged to the top of the free app rankings in Apple's U.S. App Store, overtaking ChatGPT. Users can transfer their data to Claude by exporting their chat history or manually copying key conversations.</t>
+          <t>Many users are switching to Claude due to controversies surrounding ChatGPT and OpenAI. Claude has surged to the top of the free app rankings in Apple's U.S. App Store, and daily sign-ups have hit record highs. Users can transfer their data from ChatGPT to Claude by exporting their chat history or manually copying key conversations.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Hundreds of tech workers signed an open letter urging the DOD to withdraw its designation of Anthropic as a supply-chain risk. The letter also calls on Congress to examine the use of extraordinary authorities against an American technology company. Tech workers are concerned about potential government overreach and use of AI for nefarious purposes.</t>
+          <t>Hundreds of tech workers signed an open letter urging the DOD to withdraw its designation of Anthropic as a supply-chain risk. The letter also calls on Congress to examine the use of extraordinary authorities against an American technology company. Anthropic refused to give the military unrestricted access to its AI systems due to concerns over mass surveillance and autonomous weapons.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>AI-Powered Customer Support Agency Replaces Human Teams at Startups</t>
+          <t>14.ai Replaces Customer Support Teams at Startups with AI</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>14.ai, a Y Combinator-backed startup, is revolutionizing customer support by replacing human teams with AI-powered agents. Founded by a married duo, Marie Schneegans and Michael Fester, the company has raised $3 million in seed funding and aims to increase its headcount in the next six months. With its AI-native approach, 14.ai can integrate with support systems within a day and start clearing ticket backlogs quickly.</t>
+          <t>14.ai, a Y Combinator-backed startup, is replacing legacy customer support teams at startups with its AI-native agency. The company, founded by a married duo, has raised $3 million in seed funding and aims to increase its headcount in the next six months. 14.ai combines software and services to provide efficient customer support, integrating with various channels and automating tasks to reduce human labor costs.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Anthropic's Claude Experiences Widespread Outage Due to Technical Issues</t>
+          <t>Anthropic's Claude Experiences Widespread Outage on Monday</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Anthropic's AI chatbot Claude experienced a widespread outage on Monday morning, affecting thousands of users. The company has identified an issue and is implementing a fix, but the cause of the outage remains unclear. The disruption comes after Claude rose to the top of the App Store charts, overtaking archrival ChatGPT.</t>
+          <t>Anthropic's AI chatbot, Claude, experienced a widespread outage on Monday, affecting thousands of users. The company has identified an issue and is working on a fix. The outage comes after an influx of users following the company's negotiations with the Pentagon.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Google looks to tackle longstanding RCS spam in India — but not alone</t>
+          <t>Google Tackles RCS Spam in India with Carrier Integration</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>As persistent spam complaints have clouded Google’s Rich Communication Services (RCS) push in India, the company is turning to deeper carrier integration to bolster protections on the platform. On Sunday, Bharti Airtel, India’s second-largest telecom operator with over 463 million subscribers, said it had partnered with Google to integrate the carrier’s network-level spam filtering into the RCS ecosystem in the country.</t>
+          <t>Google has partnered with Bharti Airtel to integrate carrier-level spam filtering into RCS in India, aimed at reducing unwanted messages and fraud. The move is a step towards strengthening protections on the platform, which has been plagued by spam complaints. The partnership is a global first and may be extended to other markets as Google works to standardize security across the RCS ecosystem.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Investors spill what they aren’t looking for anymore in AI SaaS companies</t>
+          <t>Investors Shun AI SaaS Companies Lacking Depth and Expertise</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Investors have been pouring billions into AI companies over the past few years, as the technology continues to hold sway in the Valley and thus the world. But not all AI companies are grabbing investor attention.</t>
+          <t>Investors are pouring billions into AI companies, but not all AI startups are grabbing attention. To remain attractive, SaaS companies need to focus on depth and expertise, with tools embedded in critical workflows. Generic productivity tools, project management software, and thin AI wrappers are no longer popular among investors.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -2444,17 +2444,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OpenAI reveals more details about its agreement with the Pentagon</t>
+          <t>OpenAI Reveals Details of Agreement with the Pentagon</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>By CEO Sam Altman’s own admission, OpenAI’s deal with the Department of Defense was “definitely rushed,” and “the optics don’t look good.” After negotiations between Anthropic and the Pentagon fell through on Friday, President Donald Trump directed federal agencies to stop using Anthropic’s technology after a six-month transition period , and Secretary of Defense Pete Hegseth said he was designating the AI company as a supply-chain risk. Then, OpenAI quickly announced that it had reached a deal of its own for models to be deployed in classified environments.</t>
+          <t>OpenAI has published a blog post outlining its approach to deploying AI models in classified environments, addressing concerns about mass domestic surveillance and autonomous weapons. The company claims its agreement with the Pentagon protects its red lines through a multi-layered approach, but critics argue the deal still allows for domestic surveillance.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
